--- a/artfynd/A 31560-2024 artfynd.xlsx
+++ b/artfynd/A 31560-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1395,10 +1395,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131244269</v>
+        <v>131244272</v>
       </c>
       <c r="B8" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,13 +1433,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>613333</v>
+        <v>613374</v>
       </c>
       <c r="R8" t="n">
-        <v>6998073</v>
+        <v>6998037</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1469,11 +1469,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom ett område på 25m</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1516,10 +1511,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131244272</v>
+        <v>131244269</v>
       </c>
       <c r="B9" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,13 +1549,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>613374</v>
+        <v>613333</v>
       </c>
       <c r="R9" t="n">
-        <v>6998037</v>
+        <v>6998073</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1590,6 +1585,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom ett område på 25m</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1635,7 +1635,7 @@
         <v>131244279</v>
       </c>
       <c r="B10" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>131244300</v>
       </c>
       <c r="B11" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>131244283</v>
       </c>
       <c r="B13" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>131244299</v>
       </c>
       <c r="B14" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>131244280</v>
       </c>
       <c r="B15" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>131244281</v>
       </c>
       <c r="B16" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,10 +2423,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131244274</v>
+        <v>131244253</v>
       </c>
       <c r="B17" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2434,26 +2434,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2461,10 +2466,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>613467</v>
+        <v>613354</v>
       </c>
       <c r="R17" t="n">
-        <v>6997940</v>
+        <v>6998128</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2499,30 +2504,19 @@
           <t>2026-02-20</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2539,10 +2533,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131244273</v>
+        <v>131244274</v>
       </c>
       <c r="B18" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2577,10 +2571,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>613476</v>
+        <v>613467</v>
       </c>
       <c r="R18" t="n">
-        <v>6997926</v>
+        <v>6997940</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2613,11 +2607,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Två tallar med rikliga mängder garnlav</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2660,10 +2649,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131244253</v>
+        <v>131244273</v>
       </c>
       <c r="B19" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2671,31 +2660,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2703,10 +2687,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>613354</v>
+        <v>613476</v>
       </c>
       <c r="R19" t="n">
-        <v>6998128</v>
+        <v>6997926</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2743,7 +2727,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Två tallar med rikliga mängder garnlav</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2752,8 +2736,24 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2770,10 +2770,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131244257</v>
+        <v>131244289</v>
       </c>
       <c r="B20" t="n">
-        <v>57881</v>
+        <v>79246</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2781,31 +2781,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2813,10 +2808,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>613343</v>
+        <v>613338</v>
       </c>
       <c r="R20" t="n">
-        <v>6998121</v>
+        <v>6998224</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2857,8 +2852,24 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2875,10 +2886,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131244289</v>
+        <v>131244257</v>
       </c>
       <c r="B21" t="n">
-        <v>79245</v>
+        <v>57881</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2886,26 +2897,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2913,10 +2929,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>613338</v>
+        <v>613343</v>
       </c>
       <c r="R21" t="n">
-        <v>6998224</v>
+        <v>6998121</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2957,24 +2973,8 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2994,7 +2994,7 @@
         <v>131244276</v>
       </c>
       <c r="B22" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>131244278</v>
       </c>
       <c r="B23" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>131244290</v>
       </c>
       <c r="B24" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v>131244288</v>
       </c>
       <c r="B25" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>131244284</v>
       </c>
       <c r="B26" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3686,10 +3686,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131244252</v>
+        <v>131244259</v>
       </c>
       <c r="B28" t="n">
-        <v>57884</v>
+        <v>92112</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3697,42 +3697,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Vallsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>613433</v>
+        <v>613387</v>
       </c>
       <c r="R28" t="n">
-        <v>6998019</v>
+        <v>6998216</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3765,11 +3757,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3796,10 +3783,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131244255</v>
+        <v>131244252</v>
       </c>
       <c r="B29" t="n">
-        <v>58043</v>
+        <v>57884</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3807,50 +3794,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Vallsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>613399</v>
+        <v>613433</v>
       </c>
       <c r="R29" t="n">
-        <v>6998197</v>
+        <v>6998019</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3880,19 +3859,14 @@
           <t>2026-02-20</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-02-20</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>10:00</t>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3919,10 +3893,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131244259</v>
+        <v>131244255</v>
       </c>
       <c r="B30" t="n">
-        <v>92111</v>
+        <v>58043</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3930,34 +3904,50 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Vallsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>613387</v>
+        <v>613399</v>
       </c>
       <c r="R30" t="n">
-        <v>6998216</v>
+        <v>6998197</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3987,9 +3977,19 @@
           <t>2026-02-20</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4019,7 +4019,7 @@
         <v>131244296</v>
       </c>
       <c r="B31" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>131244266</v>
       </c>
       <c r="B32" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
         <v>131244263</v>
       </c>
       <c r="B33" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>131244277</v>
       </c>
       <c r="B34" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>131244248</v>
       </c>
       <c r="B35" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
         <v>131244295</v>
       </c>
       <c r="B36" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4698,10 +4698,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131244297</v>
+        <v>131244250</v>
       </c>
       <c r="B37" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4709,26 +4709,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4736,10 +4741,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>613464</v>
+        <v>613387</v>
       </c>
       <c r="R37" t="n">
-        <v>6998117</v>
+        <v>6998025</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4774,30 +4779,19 @@
           <t>2026-02-20</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4814,10 +4808,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131244250</v>
+        <v>131244297</v>
       </c>
       <c r="B38" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4825,31 +4819,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4857,10 +4846,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>613387</v>
+        <v>613464</v>
       </c>
       <c r="R38" t="n">
-        <v>6998025</v>
+        <v>6998117</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4895,19 +4884,30 @@
           <t>2026-02-20</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4927,7 +4927,7 @@
         <v>131244265</v>
       </c>
       <c r="B39" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5148,6 +5148,414 @@
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>131153394</v>
+      </c>
+      <c r="B41" t="n">
+        <v>91814</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Vallsjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>613475</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6998159</v>
+      </c>
+      <c r="S41" t="n">
+        <v>25</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>131081761</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Vallsjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>613414</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6998078</v>
+      </c>
+      <c r="S42" t="n">
+        <v>25</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>131081730</v>
+      </c>
+      <c r="B43" t="n">
+        <v>91814</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Vallsjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>613416</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6998071</v>
+      </c>
+      <c r="S43" t="n">
+        <v>25</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>131081734</v>
+      </c>
+      <c r="B44" t="n">
+        <v>92112</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>658</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Vallsjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>613416</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6998071</v>
+      </c>
+      <c r="S44" t="n">
+        <v>25</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31560-2024 artfynd.xlsx
+++ b/artfynd/A 31560-2024 artfynd.xlsx
@@ -2423,10 +2423,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131244253</v>
+        <v>131244274</v>
       </c>
       <c r="B17" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2434,31 +2434,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2466,10 +2461,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>613354</v>
+        <v>613467</v>
       </c>
       <c r="R17" t="n">
-        <v>6998128</v>
+        <v>6997940</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2504,19 +2499,30 @@
           <t>2026-02-20</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2533,7 +2539,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131244274</v>
+        <v>131244273</v>
       </c>
       <c r="B18" t="n">
         <v>79246</v>
@@ -2571,10 +2577,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>613467</v>
+        <v>613476</v>
       </c>
       <c r="R18" t="n">
-        <v>6997940</v>
+        <v>6997926</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2607,6 +2613,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Två tallar med rikliga mängder garnlav</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2649,10 +2660,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131244273</v>
+        <v>131244253</v>
       </c>
       <c r="B19" t="n">
-        <v>79246</v>
+        <v>57884</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2660,26 +2671,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2687,10 +2703,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>613476</v>
+        <v>613354</v>
       </c>
       <c r="R19" t="n">
-        <v>6997926</v>
+        <v>6998128</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2727,7 +2743,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Två tallar med rikliga mängder garnlav</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2736,24 +2752,8 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -3686,10 +3686,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131244259</v>
+        <v>131244252</v>
       </c>
       <c r="B28" t="n">
-        <v>92112</v>
+        <v>57884</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3697,34 +3697,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Vallsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>613387</v>
+        <v>613433</v>
       </c>
       <c r="R28" t="n">
-        <v>6998216</v>
+        <v>6998019</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3757,6 +3765,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3783,10 +3796,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131244252</v>
+        <v>131244255</v>
       </c>
       <c r="B29" t="n">
-        <v>57884</v>
+        <v>58043</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3794,42 +3807,50 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Vallsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>613433</v>
+        <v>613399</v>
       </c>
       <c r="R29" t="n">
-        <v>6998019</v>
+        <v>6998197</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3859,14 +3880,19 @@
           <t>2026-02-20</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-02-20</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3893,10 +3919,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131244255</v>
+        <v>131244259</v>
       </c>
       <c r="B30" t="n">
-        <v>58043</v>
+        <v>92112</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3904,50 +3930,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Vallsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>613399</v>
+        <v>613387</v>
       </c>
       <c r="R30" t="n">
-        <v>6998197</v>
+        <v>6998216</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3977,19 +3987,9 @@
           <t>2026-02-20</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>10:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4698,10 +4698,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131244250</v>
+        <v>131244297</v>
       </c>
       <c r="B37" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4709,31 +4709,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4741,10 +4736,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>613387</v>
+        <v>613464</v>
       </c>
       <c r="R37" t="n">
-        <v>6998025</v>
+        <v>6998117</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4779,19 +4774,30 @@
           <t>2026-02-20</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4808,10 +4814,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131244297</v>
+        <v>131244250</v>
       </c>
       <c r="B38" t="n">
-        <v>79246</v>
+        <v>57884</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4819,26 +4825,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4846,10 +4857,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>613464</v>
+        <v>613387</v>
       </c>
       <c r="R38" t="n">
-        <v>6998117</v>
+        <v>6998025</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4884,30 +4895,19 @@
           <t>2026-02-20</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">

--- a/artfynd/A 31560-2024 artfynd.xlsx
+++ b/artfynd/A 31560-2024 artfynd.xlsx
@@ -1398,7 +1398,7 @@
         <v>131244272</v>
       </c>
       <c r="B8" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>131244269</v>
       </c>
       <c r="B9" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1632,10 +1632,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131244279</v>
+        <v>131244258</v>
       </c>
       <c r="B10" t="n">
-        <v>79246</v>
+        <v>57883</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1643,26 +1643,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1670,10 +1675,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>613427</v>
+        <v>613451</v>
       </c>
       <c r="R10" t="n">
-        <v>6998062</v>
+        <v>6998138</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1714,24 +1719,8 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1751,7 +1740,7 @@
         <v>131244300</v>
       </c>
       <c r="B11" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1864,10 +1853,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131244258</v>
+        <v>131244279</v>
       </c>
       <c r="B12" t="n">
-        <v>57881</v>
+        <v>79248</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,31 +1864,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1907,10 +1891,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>613451</v>
+        <v>613427</v>
       </c>
       <c r="R12" t="n">
-        <v>6998138</v>
+        <v>6998062</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1951,8 +1935,24 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1972,7 +1972,7 @@
         <v>131244283</v>
       </c>
       <c r="B13" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>131244299</v>
       </c>
       <c r="B14" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2201,10 +2201,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131244280</v>
+        <v>131244281</v>
       </c>
       <c r="B15" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2239,13 +2239,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>613405</v>
+        <v>613346</v>
       </c>
       <c r="R15" t="n">
-        <v>6998110</v>
+        <v>6998128</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2275,6 +2275,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikliga mängder garnlav på främst tall men även gran inom ett område på ca 50 m.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2286,21 +2291,6 @@
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2317,10 +2307,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131244281</v>
+        <v>131244280</v>
       </c>
       <c r="B16" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2355,13 +2345,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>613346</v>
+        <v>613405</v>
       </c>
       <c r="R16" t="n">
-        <v>6998128</v>
+        <v>6998110</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2391,11 +2381,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikliga mängder garnlav på främst tall men även gran inom ett område på ca 50 m.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2407,6 +2392,21 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2423,10 +2423,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131244274</v>
+        <v>131244253</v>
       </c>
       <c r="B17" t="n">
-        <v>79246</v>
+        <v>57886</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2434,26 +2434,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2461,10 +2466,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>613467</v>
+        <v>613354</v>
       </c>
       <c r="R17" t="n">
-        <v>6997940</v>
+        <v>6998128</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2499,30 +2504,19 @@
           <t>2026-02-20</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2539,10 +2533,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131244273</v>
+        <v>131244274</v>
       </c>
       <c r="B18" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2577,10 +2571,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>613476</v>
+        <v>613467</v>
       </c>
       <c r="R18" t="n">
-        <v>6997926</v>
+        <v>6997940</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2613,11 +2607,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Två tallar med rikliga mängder garnlav</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2660,10 +2649,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131244253</v>
+        <v>131244273</v>
       </c>
       <c r="B19" t="n">
-        <v>57884</v>
+        <v>79248</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2671,31 +2660,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2703,10 +2687,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>613354</v>
+        <v>613476</v>
       </c>
       <c r="R19" t="n">
-        <v>6998128</v>
+        <v>6997926</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2743,7 +2727,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Två tallar med rikliga mängder garnlav</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2752,8 +2736,24 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2773,7 +2773,7 @@
         <v>131244289</v>
       </c>
       <c r="B20" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>131244257</v>
       </c>
       <c r="B21" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2991,10 +2991,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131244276</v>
+        <v>131244278</v>
       </c>
       <c r="B22" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3029,13 +3029,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>613444</v>
+        <v>613406</v>
       </c>
       <c r="R22" t="n">
-        <v>6998014</v>
+        <v>6998050</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3065,11 +3065,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Rilkigt med garnlav inom ett ca 25m område</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3084,17 +3079,17 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3112,10 +3107,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131244278</v>
+        <v>131244276</v>
       </c>
       <c r="B23" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3150,13 +3145,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>613406</v>
+        <v>613444</v>
       </c>
       <c r="R23" t="n">
-        <v>6998050</v>
+        <v>6998014</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3186,6 +3181,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rilkigt med garnlav inom ett ca 25m område</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3200,17 +3200,17 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3228,10 +3228,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131244290</v>
+        <v>131244288</v>
       </c>
       <c r="B24" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>613327</v>
+        <v>613331</v>
       </c>
       <c r="R24" t="n">
-        <v>6998224</v>
+        <v>6998221</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3344,10 +3344,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131244288</v>
+        <v>131244290</v>
       </c>
       <c r="B25" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3382,10 +3382,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>613331</v>
+        <v>613327</v>
       </c>
       <c r="R25" t="n">
-        <v>6998221</v>
+        <v>6998224</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3463,7 +3463,7 @@
         <v>131244284</v>
       </c>
       <c r="B26" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         <v>131244251</v>
       </c>
       <c r="B27" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>131244252</v>
       </c>
       <c r="B28" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3796,10 +3796,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131244255</v>
+        <v>131244259</v>
       </c>
       <c r="B29" t="n">
-        <v>58043</v>
+        <v>92114</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3807,50 +3807,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Vallsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>613399</v>
+        <v>613387</v>
       </c>
       <c r="R29" t="n">
-        <v>6998197</v>
+        <v>6998216</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3880,19 +3864,9 @@
           <t>2026-02-20</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>10:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3919,10 +3893,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131244259</v>
+        <v>131244255</v>
       </c>
       <c r="B30" t="n">
-        <v>92112</v>
+        <v>58045</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3930,34 +3904,50 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Vallsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>613387</v>
+        <v>613399</v>
       </c>
       <c r="R30" t="n">
-        <v>6998216</v>
+        <v>6998197</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3987,9 +3977,19 @@
           <t>2026-02-20</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4019,7 +4019,7 @@
         <v>131244296</v>
       </c>
       <c r="B31" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4132,10 +4132,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131244266</v>
+        <v>131244263</v>
       </c>
       <c r="B32" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4170,13 +4170,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>613400</v>
+        <v>613379</v>
       </c>
       <c r="R32" t="n">
-        <v>6997964</v>
+        <v>6998218</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4206,6 +4206,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Rikliga mängder garnlav på gran inom ett område på 25m.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4220,17 +4225,17 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4248,10 +4253,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131244263</v>
+        <v>131244266</v>
       </c>
       <c r="B33" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4286,13 +4291,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>613379</v>
+        <v>613400</v>
       </c>
       <c r="R33" t="n">
-        <v>6998218</v>
+        <v>6997964</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4322,11 +4327,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Rikliga mängder garnlav på gran inom ett område på 25m.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4341,17 +4341,17 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4372,7 +4372,7 @@
         <v>131244277</v>
       </c>
       <c r="B34" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4485,10 +4485,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131244248</v>
+        <v>131244295</v>
       </c>
       <c r="B35" t="n">
-        <v>91814</v>
+        <v>79248</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,34 +4496,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Vallsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>613420</v>
+        <v>613437</v>
       </c>
       <c r="R35" t="n">
-        <v>6998068</v>
+        <v>6998166</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4564,8 +4567,24 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4582,10 +4601,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131244295</v>
+        <v>131244248</v>
       </c>
       <c r="B36" t="n">
-        <v>79246</v>
+        <v>91816</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4593,37 +4612,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Vallsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>613437</v>
+        <v>613420</v>
       </c>
       <c r="R36" t="n">
-        <v>6998166</v>
+        <v>6998068</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4664,24 +4680,8 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4698,10 +4698,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131244297</v>
+        <v>131244250</v>
       </c>
       <c r="B37" t="n">
-        <v>79246</v>
+        <v>57886</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4709,26 +4709,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4736,10 +4741,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>613464</v>
+        <v>613387</v>
       </c>
       <c r="R37" t="n">
-        <v>6998117</v>
+        <v>6998025</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4774,30 +4779,19 @@
           <t>2026-02-20</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4814,10 +4808,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131244250</v>
+        <v>131244297</v>
       </c>
       <c r="B38" t="n">
-        <v>57884</v>
+        <v>79248</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4825,31 +4819,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4857,10 +4846,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>613387</v>
+        <v>613464</v>
       </c>
       <c r="R38" t="n">
-        <v>6998025</v>
+        <v>6998117</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4895,19 +4884,30 @@
           <t>2026-02-20</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4927,7 +4927,7 @@
         <v>131244265</v>
       </c>
       <c r="B39" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         <v>131244262</v>
       </c>
       <c r="B40" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>131153394</v>
       </c>
       <c r="B41" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>131081761</v>
       </c>
       <c r="B42" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>131081730</v>
       </c>
       <c r="B43" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>131081734</v>
       </c>
       <c r="B44" t="n">
-        <v>92112</v>
+        <v>92114</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 31560-2024 artfynd.xlsx
+++ b/artfynd/A 31560-2024 artfynd.xlsx
@@ -1395,10 +1395,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131244272</v>
+        <v>131244269</v>
       </c>
       <c r="B8" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,13 +1433,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>613374</v>
+        <v>613333</v>
       </c>
       <c r="R8" t="n">
-        <v>6998037</v>
+        <v>6998073</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1469,6 +1469,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom ett område på 25m</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1511,10 +1516,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131244269</v>
+        <v>131244272</v>
       </c>
       <c r="B9" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,13 +1554,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>613333</v>
+        <v>613374</v>
       </c>
       <c r="R9" t="n">
-        <v>6998073</v>
+        <v>6998037</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1585,11 +1590,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom ett område på 25m</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1635,7 +1635,7 @@
         <v>131244258</v>
       </c>
       <c r="B10" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1737,10 +1737,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131244300</v>
+        <v>131244279</v>
       </c>
       <c r="B11" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>613444</v>
+        <v>613427</v>
       </c>
       <c r="R11" t="n">
-        <v>6998046</v>
+        <v>6998062</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1825,17 +1825,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1853,10 +1853,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131244279</v>
+        <v>131244300</v>
       </c>
       <c r="B12" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1891,10 +1891,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>613427</v>
+        <v>613444</v>
       </c>
       <c r="R12" t="n">
-        <v>6998062</v>
+        <v>6998046</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1941,17 +1941,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1972,7 +1972,7 @@
         <v>131244283</v>
       </c>
       <c r="B13" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>131244299</v>
       </c>
       <c r="B14" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2201,10 +2201,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131244281</v>
+        <v>131244280</v>
       </c>
       <c r="B15" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2239,13 +2239,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>613346</v>
+        <v>613405</v>
       </c>
       <c r="R15" t="n">
-        <v>6998128</v>
+        <v>6998110</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2275,11 +2275,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Rikliga mängder garnlav på främst tall men även gran inom ett område på ca 50 m.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,6 +2286,21 @@
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2307,10 +2317,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131244280</v>
+        <v>131244281</v>
       </c>
       <c r="B16" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2345,13 +2355,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>613405</v>
+        <v>613346</v>
       </c>
       <c r="R16" t="n">
-        <v>6998110</v>
+        <v>6998128</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2381,6 +2391,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikliga mängder garnlav på främst tall men även gran inom ett område på ca 50 m.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2392,21 +2407,6 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2423,10 +2423,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131244253</v>
+        <v>131244274</v>
       </c>
       <c r="B17" t="n">
-        <v>57886</v>
+        <v>79249</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2434,31 +2434,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2466,10 +2461,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>613354</v>
+        <v>613467</v>
       </c>
       <c r="R17" t="n">
-        <v>6998128</v>
+        <v>6997940</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2504,19 +2499,30 @@
           <t>2026-02-20</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2533,10 +2539,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131244274</v>
+        <v>131244273</v>
       </c>
       <c r="B18" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2571,10 +2577,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>613467</v>
+        <v>613476</v>
       </c>
       <c r="R18" t="n">
-        <v>6997940</v>
+        <v>6997926</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2607,6 +2613,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Två tallar med rikliga mängder garnlav</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2649,10 +2660,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131244273</v>
+        <v>131244253</v>
       </c>
       <c r="B19" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2660,26 +2671,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2687,10 +2703,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>613476</v>
+        <v>613354</v>
       </c>
       <c r="R19" t="n">
-        <v>6997926</v>
+        <v>6998128</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2727,7 +2743,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Två tallar med rikliga mängder garnlav</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2736,24 +2752,8 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2770,10 +2770,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131244289</v>
+        <v>131244257</v>
       </c>
       <c r="B20" t="n">
-        <v>79248</v>
+        <v>57884</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2781,26 +2781,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2808,10 +2813,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>613338</v>
+        <v>613343</v>
       </c>
       <c r="R20" t="n">
-        <v>6998224</v>
+        <v>6998121</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2852,24 +2857,8 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2886,10 +2875,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131244257</v>
+        <v>131244289</v>
       </c>
       <c r="B21" t="n">
-        <v>57883</v>
+        <v>79249</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2897,31 +2886,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2929,10 +2913,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>613343</v>
+        <v>613338</v>
       </c>
       <c r="R21" t="n">
-        <v>6998121</v>
+        <v>6998224</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2973,8 +2957,24 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2991,10 +2991,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131244278</v>
+        <v>131244276</v>
       </c>
       <c r="B22" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3029,13 +3029,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>613406</v>
+        <v>613444</v>
       </c>
       <c r="R22" t="n">
-        <v>6998050</v>
+        <v>6998014</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3065,6 +3065,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rilkigt med garnlav inom ett ca 25m område</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3079,17 +3084,17 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3107,10 +3112,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131244276</v>
+        <v>131244278</v>
       </c>
       <c r="B23" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3145,13 +3150,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>613444</v>
+        <v>613406</v>
       </c>
       <c r="R23" t="n">
-        <v>6998014</v>
+        <v>6998050</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3181,11 +3186,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Rilkigt med garnlav inom ett ca 25m område</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3200,17 +3200,17 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3228,10 +3228,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131244288</v>
+        <v>131244290</v>
       </c>
       <c r="B24" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>613331</v>
+        <v>613327</v>
       </c>
       <c r="R24" t="n">
-        <v>6998221</v>
+        <v>6998224</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3344,10 +3344,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131244290</v>
+        <v>131244288</v>
       </c>
       <c r="B25" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3382,10 +3382,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>613327</v>
+        <v>613331</v>
       </c>
       <c r="R25" t="n">
-        <v>6998224</v>
+        <v>6998221</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3463,7 +3463,7 @@
         <v>131244284</v>
       </c>
       <c r="B26" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         <v>131244251</v>
       </c>
       <c r="B27" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3686,10 +3686,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131244252</v>
+        <v>131244259</v>
       </c>
       <c r="B28" t="n">
-        <v>57886</v>
+        <v>92115</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3697,42 +3697,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Vallsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>613433</v>
+        <v>613387</v>
       </c>
       <c r="R28" t="n">
-        <v>6998019</v>
+        <v>6998216</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3765,11 +3757,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3796,10 +3783,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131244259</v>
+        <v>131244255</v>
       </c>
       <c r="B29" t="n">
-        <v>92114</v>
+        <v>58046</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3807,34 +3794,50 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Vallsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>613387</v>
+        <v>613399</v>
       </c>
       <c r="R29" t="n">
-        <v>6998216</v>
+        <v>6998197</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3864,9 +3867,19 @@
           <t>2026-02-20</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3893,10 +3906,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131244255</v>
+        <v>131244252</v>
       </c>
       <c r="B30" t="n">
-        <v>58045</v>
+        <v>57887</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3904,50 +3917,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Vallsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>613399</v>
+        <v>613433</v>
       </c>
       <c r="R30" t="n">
-        <v>6998197</v>
+        <v>6998019</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3977,19 +3982,14 @@
           <t>2026-02-20</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-02-20</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>10:00</t>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4019,7 +4019,7 @@
         <v>131244296</v>
       </c>
       <c r="B31" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4132,10 +4132,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131244263</v>
+        <v>131244266</v>
       </c>
       <c r="B32" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4170,13 +4170,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>613379</v>
+        <v>613400</v>
       </c>
       <c r="R32" t="n">
-        <v>6998218</v>
+        <v>6997964</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4206,11 +4206,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Rikliga mängder garnlav på gran inom ett område på 25m.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4225,17 +4220,17 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4253,10 +4248,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131244266</v>
+        <v>131244263</v>
       </c>
       <c r="B33" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4291,13 +4286,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>613400</v>
+        <v>613379</v>
       </c>
       <c r="R33" t="n">
-        <v>6997964</v>
+        <v>6998218</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4327,6 +4322,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rikliga mängder garnlav på gran inom ett område på 25m.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4341,17 +4341,17 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4372,7 +4372,7 @@
         <v>131244277</v>
       </c>
       <c r="B34" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>131244295</v>
       </c>
       <c r="B35" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>131244248</v>
       </c>
       <c r="B36" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4698,10 +4698,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131244250</v>
+        <v>131244297</v>
       </c>
       <c r="B37" t="n">
-        <v>57886</v>
+        <v>79249</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4709,31 +4709,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4741,10 +4736,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>613387</v>
+        <v>613464</v>
       </c>
       <c r="R37" t="n">
-        <v>6998025</v>
+        <v>6998117</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4779,19 +4774,30 @@
           <t>2026-02-20</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4808,10 +4814,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131244297</v>
+        <v>131244250</v>
       </c>
       <c r="B38" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4819,26 +4825,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4846,10 +4857,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>613464</v>
+        <v>613387</v>
       </c>
       <c r="R38" t="n">
-        <v>6998117</v>
+        <v>6998025</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4884,30 +4895,19 @@
           <t>2026-02-20</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4927,7 +4927,7 @@
         <v>131244265</v>
       </c>
       <c r="B39" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         <v>131244262</v>
       </c>
       <c r="B40" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>131153394</v>
       </c>
       <c r="B41" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>131081761</v>
       </c>
       <c r="B42" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>131081730</v>
       </c>
       <c r="B43" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>131081734</v>
       </c>
       <c r="B44" t="n">
-        <v>92114</v>
+        <v>92115</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 31560-2024 artfynd.xlsx
+++ b/artfynd/A 31560-2024 artfynd.xlsx
@@ -1632,10 +1632,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131244258</v>
+        <v>131244279</v>
       </c>
       <c r="B10" t="n">
-        <v>57884</v>
+        <v>79249</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1643,31 +1643,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1675,10 +1670,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>613451</v>
+        <v>613427</v>
       </c>
       <c r="R10" t="n">
-        <v>6998138</v>
+        <v>6998062</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1719,8 +1714,24 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1737,7 +1748,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131244279</v>
+        <v>131244300</v>
       </c>
       <c r="B11" t="n">
         <v>79249</v>
@@ -1775,10 +1786,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>613427</v>
+        <v>613444</v>
       </c>
       <c r="R11" t="n">
-        <v>6998062</v>
+        <v>6998046</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1825,17 +1836,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1853,10 +1864,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131244300</v>
+        <v>131244258</v>
       </c>
       <c r="B12" t="n">
-        <v>79249</v>
+        <v>57884</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,26 +1875,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1891,10 +1907,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>613444</v>
+        <v>613451</v>
       </c>
       <c r="R12" t="n">
-        <v>6998046</v>
+        <v>6998138</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1935,24 +1951,8 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -3783,10 +3783,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131244255</v>
+        <v>131244252</v>
       </c>
       <c r="B29" t="n">
-        <v>58046</v>
+        <v>57887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3794,50 +3794,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Vallsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>613399</v>
+        <v>613433</v>
       </c>
       <c r="R29" t="n">
-        <v>6998197</v>
+        <v>6998019</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3867,19 +3859,14 @@
           <t>2026-02-20</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-02-20</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>10:00</t>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3906,10 +3893,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131244252</v>
+        <v>131244255</v>
       </c>
       <c r="B30" t="n">
-        <v>57887</v>
+        <v>58046</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3917,42 +3904,50 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Vallsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>613433</v>
+        <v>613399</v>
       </c>
       <c r="R30" t="n">
-        <v>6998019</v>
+        <v>6998197</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3982,14 +3977,19 @@
           <t>2026-02-20</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-02-20</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4016,7 +4016,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131244296</v>
+        <v>131244266</v>
       </c>
       <c r="B31" t="n">
         <v>79249</v>
@@ -4054,10 +4054,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>613453</v>
+        <v>613400</v>
       </c>
       <c r="R31" t="n">
-        <v>6998141</v>
+        <v>6997964</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4132,7 +4132,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131244266</v>
+        <v>131244263</v>
       </c>
       <c r="B32" t="n">
         <v>79249</v>
@@ -4170,13 +4170,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>613400</v>
+        <v>613379</v>
       </c>
       <c r="R32" t="n">
-        <v>6997964</v>
+        <v>6998218</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4206,6 +4206,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Rikliga mängder garnlav på gran inom ett område på 25m.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4220,17 +4225,17 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4248,7 +4253,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131244263</v>
+        <v>131244296</v>
       </c>
       <c r="B33" t="n">
         <v>79249</v>
@@ -4286,13 +4291,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>613379</v>
+        <v>613453</v>
       </c>
       <c r="R33" t="n">
-        <v>6998218</v>
+        <v>6998141</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4322,11 +4327,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Rikliga mängder garnlav på gran inom ett område på 25m.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4341,17 +4341,17 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4485,10 +4485,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131244295</v>
+        <v>131244248</v>
       </c>
       <c r="B35" t="n">
-        <v>79249</v>
+        <v>91817</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,37 +4496,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Vallsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>613437</v>
+        <v>613420</v>
       </c>
       <c r="R35" t="n">
-        <v>6998166</v>
+        <v>6998068</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4567,24 +4564,8 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4601,10 +4582,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131244248</v>
+        <v>131244295</v>
       </c>
       <c r="B36" t="n">
-        <v>91817</v>
+        <v>79249</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4612,34 +4593,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Vallsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>613420</v>
+        <v>613437</v>
       </c>
       <c r="R36" t="n">
-        <v>6998068</v>
+        <v>6998166</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4680,8 +4664,24 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">

--- a/artfynd/A 31560-2024 artfynd.xlsx
+++ b/artfynd/A 31560-2024 artfynd.xlsx
@@ -4016,7 +4016,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131244266</v>
+        <v>131244296</v>
       </c>
       <c r="B31" t="n">
         <v>79249</v>
@@ -4054,10 +4054,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>613400</v>
+        <v>613453</v>
       </c>
       <c r="R31" t="n">
-        <v>6997964</v>
+        <v>6998141</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4132,7 +4132,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131244263</v>
+        <v>131244266</v>
       </c>
       <c r="B32" t="n">
         <v>79249</v>
@@ -4170,13 +4170,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>613379</v>
+        <v>613400</v>
       </c>
       <c r="R32" t="n">
-        <v>6998218</v>
+        <v>6997964</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4206,11 +4206,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Rikliga mängder garnlav på gran inom ett område på 25m.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4225,17 +4220,17 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4253,7 +4248,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131244296</v>
+        <v>131244263</v>
       </c>
       <c r="B33" t="n">
         <v>79249</v>
@@ -4291,13 +4286,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>613453</v>
+        <v>613379</v>
       </c>
       <c r="R33" t="n">
-        <v>6998141</v>
+        <v>6998218</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4327,6 +4322,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rikliga mängder garnlav på gran inom ett område på 25m.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4341,17 +4341,17 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4698,10 +4698,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131244297</v>
+        <v>131244250</v>
       </c>
       <c r="B37" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4709,26 +4709,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4736,10 +4741,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>613464</v>
+        <v>613387</v>
       </c>
       <c r="R37" t="n">
-        <v>6998117</v>
+        <v>6998025</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4774,30 +4779,19 @@
           <t>2026-02-20</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4814,10 +4808,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131244250</v>
+        <v>131244297</v>
       </c>
       <c r="B38" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4825,31 +4819,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4857,10 +4846,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>613387</v>
+        <v>613464</v>
       </c>
       <c r="R38" t="n">
-        <v>6998025</v>
+        <v>6998117</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4895,19 +4884,30 @@
           <t>2026-02-20</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">

--- a/artfynd/A 31560-2024 artfynd.xlsx
+++ b/artfynd/A 31560-2024 artfynd.xlsx
@@ -1398,7 +1398,7 @@
         <v>131244269</v>
       </c>
       <c r="B8" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>131244272</v>
       </c>
       <c r="B9" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>131244279</v>
       </c>
       <c r="B10" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>131244300</v>
       </c>
       <c r="B11" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>131244258</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>131244283</v>
       </c>
       <c r="B13" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>131244299</v>
       </c>
       <c r="B14" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>131244280</v>
       </c>
       <c r="B15" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>131244281</v>
       </c>
       <c r="B16" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,10 +2423,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131244274</v>
+        <v>131244253</v>
       </c>
       <c r="B17" t="n">
-        <v>79249</v>
+        <v>57888</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2434,26 +2434,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2461,10 +2466,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>613467</v>
+        <v>613354</v>
       </c>
       <c r="R17" t="n">
-        <v>6997940</v>
+        <v>6998128</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2499,30 +2504,19 @@
           <t>2026-02-20</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2539,10 +2533,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131244273</v>
+        <v>131244274</v>
       </c>
       <c r="B18" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2577,10 +2571,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>613476</v>
+        <v>613467</v>
       </c>
       <c r="R18" t="n">
-        <v>6997926</v>
+        <v>6997940</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2613,11 +2607,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Två tallar med rikliga mängder garnlav</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2660,10 +2649,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131244253</v>
+        <v>131244273</v>
       </c>
       <c r="B19" t="n">
-        <v>57887</v>
+        <v>79250</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2671,31 +2660,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2703,10 +2687,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>613354</v>
+        <v>613476</v>
       </c>
       <c r="R19" t="n">
-        <v>6998128</v>
+        <v>6997926</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2743,7 +2727,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Två tallar med rikliga mängder garnlav</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2752,8 +2736,24 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2770,10 +2770,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131244257</v>
+        <v>131244289</v>
       </c>
       <c r="B20" t="n">
-        <v>57884</v>
+        <v>79250</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2781,31 +2781,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2813,10 +2808,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>613343</v>
+        <v>613338</v>
       </c>
       <c r="R20" t="n">
-        <v>6998121</v>
+        <v>6998224</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2857,8 +2852,24 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2875,10 +2886,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131244289</v>
+        <v>131244257</v>
       </c>
       <c r="B21" t="n">
-        <v>79249</v>
+        <v>57885</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2886,26 +2897,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2913,10 +2929,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>613338</v>
+        <v>613343</v>
       </c>
       <c r="R21" t="n">
-        <v>6998224</v>
+        <v>6998121</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2957,24 +2973,8 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2994,7 +2994,7 @@
         <v>131244276</v>
       </c>
       <c r="B22" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>131244278</v>
       </c>
       <c r="B23" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>131244290</v>
       </c>
       <c r="B24" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v>131244288</v>
       </c>
       <c r="B25" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>131244284</v>
       </c>
       <c r="B26" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         <v>131244251</v>
       </c>
       <c r="B27" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>131244259</v>
       </c>
       <c r="B28" t="n">
-        <v>92115</v>
+        <v>92116</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
         <v>131244252</v>
       </c>
       <c r="B29" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>131244255</v>
       </c>
       <c r="B30" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>131244296</v>
       </c>
       <c r="B31" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>131244266</v>
       </c>
       <c r="B32" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
         <v>131244263</v>
       </c>
       <c r="B33" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>131244277</v>
       </c>
       <c r="B34" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>131244248</v>
       </c>
       <c r="B35" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
         <v>131244295</v>
       </c>
       <c r="B36" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4698,10 +4698,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131244250</v>
+        <v>131244297</v>
       </c>
       <c r="B37" t="n">
-        <v>57887</v>
+        <v>79250</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4709,31 +4709,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4741,10 +4736,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>613387</v>
+        <v>613464</v>
       </c>
       <c r="R37" t="n">
-        <v>6998025</v>
+        <v>6998117</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4779,19 +4774,30 @@
           <t>2026-02-20</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4808,10 +4814,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131244297</v>
+        <v>131244250</v>
       </c>
       <c r="B38" t="n">
-        <v>79249</v>
+        <v>57888</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4819,26 +4825,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4846,10 +4857,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>613464</v>
+        <v>613387</v>
       </c>
       <c r="R38" t="n">
-        <v>6998117</v>
+        <v>6998025</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4884,30 +4895,19 @@
           <t>2026-02-20</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4927,7 +4927,7 @@
         <v>131244265</v>
       </c>
       <c r="B39" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         <v>131244262</v>
       </c>
       <c r="B40" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>131153394</v>
       </c>
       <c r="B41" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>131081761</v>
       </c>
       <c r="B42" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>131081730</v>
       </c>
       <c r="B43" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>131081734</v>
       </c>
       <c r="B44" t="n">
-        <v>92115</v>
+        <v>92116</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 31560-2024 artfynd.xlsx
+++ b/artfynd/A 31560-2024 artfynd.xlsx
@@ -1395,7 +1395,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131244269</v>
+        <v>131244272</v>
       </c>
       <c r="B8" t="n">
         <v>79250</v>
@@ -1433,13 +1433,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>613333</v>
+        <v>613374</v>
       </c>
       <c r="R8" t="n">
-        <v>6998073</v>
+        <v>6998037</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1469,11 +1469,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom ett område på 25m</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1516,7 +1511,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131244272</v>
+        <v>131244269</v>
       </c>
       <c r="B9" t="n">
         <v>79250</v>
@@ -1554,13 +1549,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>613374</v>
+        <v>613333</v>
       </c>
       <c r="R9" t="n">
-        <v>6998037</v>
+        <v>6998073</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1590,6 +1585,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom ett område på 25m</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2201,7 +2201,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131244280</v>
+        <v>131244281</v>
       </c>
       <c r="B15" t="n">
         <v>79250</v>
@@ -2239,13 +2239,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>613405</v>
+        <v>613346</v>
       </c>
       <c r="R15" t="n">
-        <v>6998110</v>
+        <v>6998128</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2275,6 +2275,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikliga mängder garnlav på främst tall men även gran inom ett område på ca 50 m.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2286,21 +2291,6 @@
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2317,7 +2307,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131244281</v>
+        <v>131244280</v>
       </c>
       <c r="B16" t="n">
         <v>79250</v>
@@ -2355,13 +2345,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>613346</v>
+        <v>613405</v>
       </c>
       <c r="R16" t="n">
-        <v>6998128</v>
+        <v>6998110</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2391,11 +2381,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikliga mängder garnlav på främst tall men även gran inom ett område på ca 50 m.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2407,6 +2392,21 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2423,10 +2423,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131244253</v>
+        <v>131244273</v>
       </c>
       <c r="B17" t="n">
-        <v>57888</v>
+        <v>79250</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2434,31 +2434,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2466,10 +2461,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>613354</v>
+        <v>613476</v>
       </c>
       <c r="R17" t="n">
-        <v>6998128</v>
+        <v>6997926</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2506,7 +2501,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Två tallar med rikliga mängder garnlav</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2515,8 +2510,24 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2649,10 +2660,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131244273</v>
+        <v>131244253</v>
       </c>
       <c r="B19" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2660,26 +2671,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2687,10 +2703,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>613476</v>
+        <v>613354</v>
       </c>
       <c r="R19" t="n">
-        <v>6997926</v>
+        <v>6998128</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2727,7 +2743,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Två tallar med rikliga mängder garnlav</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2736,24 +2752,8 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -4485,10 +4485,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131244248</v>
+        <v>131244295</v>
       </c>
       <c r="B35" t="n">
-        <v>91818</v>
+        <v>79250</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,34 +4496,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Vallsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>613420</v>
+        <v>613437</v>
       </c>
       <c r="R35" t="n">
-        <v>6998068</v>
+        <v>6998166</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4564,8 +4567,24 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4582,10 +4601,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131244295</v>
+        <v>131244248</v>
       </c>
       <c r="B36" t="n">
-        <v>79250</v>
+        <v>91818</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4593,37 +4612,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Vallsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>613437</v>
+        <v>613420</v>
       </c>
       <c r="R36" t="n">
-        <v>6998166</v>
+        <v>6998068</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4664,24 +4680,8 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">

--- a/artfynd/A 31560-2024 artfynd.xlsx
+++ b/artfynd/A 31560-2024 artfynd.xlsx
@@ -1395,7 +1395,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131244272</v>
+        <v>131244269</v>
       </c>
       <c r="B8" t="n">
         <v>79250</v>
@@ -1433,13 +1433,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>613374</v>
+        <v>613333</v>
       </c>
       <c r="R8" t="n">
-        <v>6998037</v>
+        <v>6998073</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1469,6 +1469,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom ett område på 25m</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1511,7 +1516,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131244269</v>
+        <v>131244272</v>
       </c>
       <c r="B9" t="n">
         <v>79250</v>
@@ -1549,13 +1554,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>613333</v>
+        <v>613374</v>
       </c>
       <c r="R9" t="n">
-        <v>6998073</v>
+        <v>6998037</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1585,11 +1590,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom ett område på 25m</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2770,10 +2770,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131244289</v>
+        <v>131244257</v>
       </c>
       <c r="B20" t="n">
-        <v>79250</v>
+        <v>57885</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2781,26 +2781,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2808,10 +2813,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>613338</v>
+        <v>613343</v>
       </c>
       <c r="R20" t="n">
-        <v>6998224</v>
+        <v>6998121</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2852,24 +2857,8 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2886,10 +2875,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131244257</v>
+        <v>131244289</v>
       </c>
       <c r="B21" t="n">
-        <v>57885</v>
+        <v>79250</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2897,31 +2886,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2929,10 +2913,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>613343</v>
+        <v>613338</v>
       </c>
       <c r="R21" t="n">
-        <v>6998121</v>
+        <v>6998224</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2973,8 +2957,24 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2991,7 +2991,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131244276</v>
+        <v>131244278</v>
       </c>
       <c r="B22" t="n">
         <v>79250</v>
@@ -3029,13 +3029,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>613444</v>
+        <v>613406</v>
       </c>
       <c r="R22" t="n">
-        <v>6998014</v>
+        <v>6998050</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3065,11 +3065,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Rilkigt med garnlav inom ett ca 25m område</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3084,17 +3079,17 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3112,7 +3107,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131244278</v>
+        <v>131244276</v>
       </c>
       <c r="B23" t="n">
         <v>79250</v>
@@ -3150,13 +3145,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>613406</v>
+        <v>613444</v>
       </c>
       <c r="R23" t="n">
-        <v>6998050</v>
+        <v>6998014</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3186,6 +3181,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rilkigt med garnlav inom ett ca 25m område</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3200,17 +3200,17 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>

--- a/artfynd/A 31560-2024 artfynd.xlsx
+++ b/artfynd/A 31560-2024 artfynd.xlsx
@@ -1398,7 +1398,7 @@
         <v>131244269</v>
       </c>
       <c r="B8" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>131244272</v>
       </c>
       <c r="B9" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1632,10 +1632,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131244279</v>
+        <v>131244300</v>
       </c>
       <c r="B10" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1670,10 +1670,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>613427</v>
+        <v>613444</v>
       </c>
       <c r="R10" t="n">
-        <v>6998062</v>
+        <v>6998046</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1720,17 +1720,17 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1748,10 +1748,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131244300</v>
+        <v>131244279</v>
       </c>
       <c r="B11" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>613444</v>
+        <v>613427</v>
       </c>
       <c r="R11" t="n">
-        <v>6998046</v>
+        <v>6998062</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1836,17 +1836,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1867,7 +1867,7 @@
         <v>131244258</v>
       </c>
       <c r="B12" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>131244283</v>
       </c>
       <c r="B13" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>131244299</v>
       </c>
       <c r="B14" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2201,10 +2201,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131244281</v>
+        <v>131244280</v>
       </c>
       <c r="B15" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2239,13 +2239,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>613346</v>
+        <v>613405</v>
       </c>
       <c r="R15" t="n">
-        <v>6998128</v>
+        <v>6998110</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2275,11 +2275,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Rikliga mängder garnlav på främst tall men även gran inom ett område på ca 50 m.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,6 +2286,21 @@
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2307,10 +2317,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131244280</v>
+        <v>131244281</v>
       </c>
       <c r="B16" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2345,13 +2355,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>613405</v>
+        <v>613346</v>
       </c>
       <c r="R16" t="n">
-        <v>6998110</v>
+        <v>6998128</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2381,6 +2391,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikliga mängder garnlav på främst tall men även gran inom ett område på ca 50 m.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2392,21 +2407,6 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2423,10 +2423,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131244273</v>
+        <v>131244274</v>
       </c>
       <c r="B17" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>613476</v>
+        <v>613467</v>
       </c>
       <c r="R17" t="n">
-        <v>6997926</v>
+        <v>6997940</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2497,11 +2497,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Två tallar med rikliga mängder garnlav</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2544,10 +2539,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131244274</v>
+        <v>131244253</v>
       </c>
       <c r="B18" t="n">
-        <v>79250</v>
+        <v>57891</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2555,26 +2550,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2582,10 +2582,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>613467</v>
+        <v>613354</v>
       </c>
       <c r="R18" t="n">
-        <v>6997940</v>
+        <v>6998128</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2620,30 +2620,19 @@
           <t>2026-02-20</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2660,10 +2649,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131244253</v>
+        <v>131244273</v>
       </c>
       <c r="B19" t="n">
-        <v>57888</v>
+        <v>79253</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2671,31 +2660,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2703,10 +2687,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>613354</v>
+        <v>613476</v>
       </c>
       <c r="R19" t="n">
-        <v>6998128</v>
+        <v>6997926</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2743,7 +2727,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Två tallar med rikliga mängder garnlav</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2752,8 +2736,24 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2770,10 +2770,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131244257</v>
+        <v>131244289</v>
       </c>
       <c r="B20" t="n">
-        <v>57885</v>
+        <v>79253</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2781,31 +2781,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2813,10 +2808,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>613343</v>
+        <v>613338</v>
       </c>
       <c r="R20" t="n">
-        <v>6998121</v>
+        <v>6998224</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2857,8 +2852,24 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2875,10 +2886,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131244289</v>
+        <v>131244257</v>
       </c>
       <c r="B21" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2886,26 +2897,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2913,10 +2929,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>613338</v>
+        <v>613343</v>
       </c>
       <c r="R21" t="n">
-        <v>6998224</v>
+        <v>6998121</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2957,24 +2973,8 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2991,10 +2991,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131244278</v>
+        <v>131244276</v>
       </c>
       <c r="B22" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3029,13 +3029,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>613406</v>
+        <v>613444</v>
       </c>
       <c r="R22" t="n">
-        <v>6998050</v>
+        <v>6998014</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3065,6 +3065,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rilkigt med garnlav inom ett ca 25m område</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3079,17 +3084,17 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3107,10 +3112,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131244276</v>
+        <v>131244278</v>
       </c>
       <c r="B23" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3145,13 +3150,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>613444</v>
+        <v>613406</v>
       </c>
       <c r="R23" t="n">
-        <v>6998014</v>
+        <v>6998050</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3181,11 +3186,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Rilkigt med garnlav inom ett ca 25m område</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3200,17 +3200,17 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3231,7 +3231,7 @@
         <v>131244290</v>
       </c>
       <c r="B24" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
         <v>131244288</v>
       </c>
       <c r="B25" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>131244284</v>
       </c>
       <c r="B26" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         <v>131244251</v>
       </c>
       <c r="B27" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3686,10 +3686,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131244259</v>
+        <v>131244255</v>
       </c>
       <c r="B28" t="n">
-        <v>92116</v>
+        <v>58050</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3697,34 +3697,50 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Vallsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>613387</v>
+        <v>613399</v>
       </c>
       <c r="R28" t="n">
-        <v>6998216</v>
+        <v>6998197</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3754,9 +3770,19 @@
           <t>2026-02-20</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3786,7 +3812,7 @@
         <v>131244252</v>
       </c>
       <c r="B29" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3893,10 +3919,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131244255</v>
+        <v>131244259</v>
       </c>
       <c r="B30" t="n">
-        <v>58047</v>
+        <v>92119</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3904,50 +3930,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Vallsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>613399</v>
+        <v>613387</v>
       </c>
       <c r="R30" t="n">
-        <v>6998197</v>
+        <v>6998216</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3977,19 +3987,9 @@
           <t>2026-02-20</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>09:50</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>10:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4019,7 +4019,7 @@
         <v>131244296</v>
       </c>
       <c r="B31" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>131244266</v>
       </c>
       <c r="B32" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
         <v>131244263</v>
       </c>
       <c r="B33" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>131244277</v>
       </c>
       <c r="B34" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         <v>131244295</v>
       </c>
       <c r="B35" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>131244248</v>
       </c>
       <c r="B36" t="n">
-        <v>91818</v>
+        <v>91821</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4698,10 +4698,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131244297</v>
+        <v>131244250</v>
       </c>
       <c r="B37" t="n">
-        <v>79250</v>
+        <v>57891</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4709,26 +4709,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4736,10 +4741,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>613464</v>
+        <v>613387</v>
       </c>
       <c r="R37" t="n">
-        <v>6998117</v>
+        <v>6998025</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4774,30 +4779,19 @@
           <t>2026-02-20</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4814,10 +4808,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131244250</v>
+        <v>131244297</v>
       </c>
       <c r="B38" t="n">
-        <v>57888</v>
+        <v>79253</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4825,31 +4819,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4857,10 +4846,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>613387</v>
+        <v>613464</v>
       </c>
       <c r="R38" t="n">
-        <v>6998025</v>
+        <v>6998117</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4895,19 +4884,30 @@
           <t>2026-02-20</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4927,7 +4927,7 @@
         <v>131244265</v>
       </c>
       <c r="B39" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         <v>131244262</v>
       </c>
       <c r="B40" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>131153394</v>
       </c>
       <c r="B41" t="n">
-        <v>91818</v>
+        <v>91821</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>131081761</v>
       </c>
       <c r="B42" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>131081730</v>
       </c>
       <c r="B43" t="n">
-        <v>91818</v>
+        <v>91821</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>131081734</v>
       </c>
       <c r="B44" t="n">
-        <v>92116</v>
+        <v>92119</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 31560-2024 artfynd.xlsx
+++ b/artfynd/A 31560-2024 artfynd.xlsx
@@ -1398,7 +1398,7 @@
         <v>131244269</v>
       </c>
       <c r="B8" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
         <v>131244272</v>
       </c>
       <c r="B9" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1632,10 +1632,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131244300</v>
+        <v>131244279</v>
       </c>
       <c r="B10" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1670,10 +1670,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>613444</v>
+        <v>613427</v>
       </c>
       <c r="R10" t="n">
-        <v>6998046</v>
+        <v>6998062</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1720,17 +1720,17 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1748,10 +1748,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131244279</v>
+        <v>131244300</v>
       </c>
       <c r="B11" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1786,10 +1786,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>613427</v>
+        <v>613444</v>
       </c>
       <c r="R11" t="n">
-        <v>6998062</v>
+        <v>6998046</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1836,17 +1836,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1867,7 +1867,7 @@
         <v>131244258</v>
       </c>
       <c r="B12" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>131244283</v>
       </c>
       <c r="B13" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>131244299</v>
       </c>
       <c r="B14" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>131244280</v>
       </c>
       <c r="B15" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>131244281</v>
       </c>
       <c r="B16" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,10 +2423,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131244274</v>
+        <v>131244273</v>
       </c>
       <c r="B17" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>613467</v>
+        <v>613476</v>
       </c>
       <c r="R17" t="n">
-        <v>6997940</v>
+        <v>6997926</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2497,6 +2497,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Två tallar med rikliga mängder garnlav</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2539,10 +2544,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131244253</v>
+        <v>131244274</v>
       </c>
       <c r="B18" t="n">
-        <v>57891</v>
+        <v>79254</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2550,31 +2555,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2582,10 +2582,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>613354</v>
+        <v>613467</v>
       </c>
       <c r="R18" t="n">
-        <v>6998128</v>
+        <v>6997940</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2620,19 +2620,30 @@
           <t>2026-02-20</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2649,10 +2660,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131244273</v>
+        <v>131244253</v>
       </c>
       <c r="B19" t="n">
-        <v>79253</v>
+        <v>57892</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2660,26 +2671,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2687,10 +2703,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>613476</v>
+        <v>613354</v>
       </c>
       <c r="R19" t="n">
-        <v>6997926</v>
+        <v>6998128</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2727,7 +2743,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Två tallar med rikliga mängder garnlav</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2736,24 +2752,8 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2773,7 +2773,7 @@
         <v>131244289</v>
       </c>
       <c r="B20" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>131244257</v>
       </c>
       <c r="B21" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>131244276</v>
       </c>
       <c r="B22" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>131244278</v>
       </c>
       <c r="B23" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3228,10 +3228,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131244290</v>
+        <v>131244288</v>
       </c>
       <c r="B24" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>613327</v>
+        <v>613331</v>
       </c>
       <c r="R24" t="n">
-        <v>6998224</v>
+        <v>6998221</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3344,10 +3344,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131244288</v>
+        <v>131244290</v>
       </c>
       <c r="B25" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3382,10 +3382,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>613331</v>
+        <v>613327</v>
       </c>
       <c r="R25" t="n">
-        <v>6998221</v>
+        <v>6998224</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3463,7 +3463,7 @@
         <v>131244284</v>
       </c>
       <c r="B26" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         <v>131244251</v>
       </c>
       <c r="B27" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>131244255</v>
       </c>
       <c r="B28" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3809,10 +3809,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131244252</v>
+        <v>131244259</v>
       </c>
       <c r="B29" t="n">
-        <v>57891</v>
+        <v>92120</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3820,42 +3820,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Vallsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>613433</v>
+        <v>613387</v>
       </c>
       <c r="R29" t="n">
-        <v>6998019</v>
+        <v>6998216</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3888,11 +3880,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-02-20</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3919,10 +3906,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131244259</v>
+        <v>131244252</v>
       </c>
       <c r="B30" t="n">
-        <v>92119</v>
+        <v>57892</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3930,34 +3917,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Vallsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>613387</v>
+        <v>613433</v>
       </c>
       <c r="R30" t="n">
-        <v>6998216</v>
+        <v>6998019</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3990,6 +3985,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4019,7 +4019,7 @@
         <v>131244296</v>
       </c>
       <c r="B31" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>131244266</v>
       </c>
       <c r="B32" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
         <v>131244263</v>
       </c>
       <c r="B33" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>131244277</v>
       </c>
       <c r="B34" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4485,10 +4485,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131244295</v>
+        <v>131244248</v>
       </c>
       <c r="B35" t="n">
-        <v>79253</v>
+        <v>91822</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4496,37 +4496,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Vallsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>613437</v>
+        <v>613420</v>
       </c>
       <c r="R35" t="n">
-        <v>6998166</v>
+        <v>6998068</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4567,24 +4564,8 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4601,10 +4582,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131244248</v>
+        <v>131244295</v>
       </c>
       <c r="B36" t="n">
-        <v>91821</v>
+        <v>79254</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4612,34 +4593,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Vallsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>613420</v>
+        <v>613437</v>
       </c>
       <c r="R36" t="n">
-        <v>6998068</v>
+        <v>6998166</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4680,8 +4664,24 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4701,7 +4701,7 @@
         <v>131244250</v>
       </c>
       <c r="B37" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>131244297</v>
       </c>
       <c r="B38" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         <v>131244265</v>
       </c>
       <c r="B39" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         <v>131244262</v>
       </c>
       <c r="B40" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>131153394</v>
       </c>
       <c r="B41" t="n">
-        <v>91821</v>
+        <v>91822</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>131081761</v>
       </c>
       <c r="B42" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>131081730</v>
       </c>
       <c r="B43" t="n">
-        <v>91821</v>
+        <v>91822</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>131081734</v>
       </c>
       <c r="B44" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 31560-2024 artfynd.xlsx
+++ b/artfynd/A 31560-2024 artfynd.xlsx
@@ -1632,10 +1632,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131244279</v>
+        <v>131244258</v>
       </c>
       <c r="B10" t="n">
-        <v>79254</v>
+        <v>57889</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1643,26 +1643,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1670,10 +1675,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>613427</v>
+        <v>613451</v>
       </c>
       <c r="R10" t="n">
-        <v>6998062</v>
+        <v>6998138</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1714,24 +1719,8 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1748,7 +1737,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131244300</v>
+        <v>131244279</v>
       </c>
       <c r="B11" t="n">
         <v>79254</v>
@@ -1786,10 +1775,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>613444</v>
+        <v>613427</v>
       </c>
       <c r="R11" t="n">
-        <v>6998046</v>
+        <v>6998062</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1836,17 +1825,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1864,10 +1853,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131244258</v>
+        <v>131244300</v>
       </c>
       <c r="B12" t="n">
-        <v>57889</v>
+        <v>79254</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1875,31 +1864,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1907,10 +1891,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>613451</v>
+        <v>613444</v>
       </c>
       <c r="R12" t="n">
-        <v>6998138</v>
+        <v>6998046</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1951,8 +1935,24 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2544,10 +2544,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131244274</v>
+        <v>131244253</v>
       </c>
       <c r="B18" t="n">
-        <v>79254</v>
+        <v>57892</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2555,26 +2555,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2582,10 +2587,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>613467</v>
+        <v>613354</v>
       </c>
       <c r="R18" t="n">
-        <v>6997940</v>
+        <v>6998128</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2620,30 +2625,19 @@
           <t>2026-02-20</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2660,10 +2654,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131244253</v>
+        <v>131244274</v>
       </c>
       <c r="B19" t="n">
-        <v>57892</v>
+        <v>79254</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2671,31 +2665,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2703,10 +2692,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>613354</v>
+        <v>613467</v>
       </c>
       <c r="R19" t="n">
-        <v>6998128</v>
+        <v>6997940</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2741,19 +2730,30 @@
           <t>2026-02-20</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
